--- a/07.excel/04.text functions in excel.xlsx
+++ b/07.excel/04.text functions in excel.xlsx
@@ -1,25 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eurov\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D5E9D3A-79FF-4714-8295-4BDE9242E7A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{ED6D2882-9879-4DFB-91DC-F0A951F83C0A}"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -27,6 +18,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="156">
   <si>
     <t>ID</t>
   </si>
@@ -60,6 +53,39 @@
     <t>Remarks</t>
   </si>
   <si>
+    <t>upper</t>
+  </si>
+  <si>
+    <t>lower</t>
+  </si>
+  <si>
+    <t>proper</t>
+  </si>
+  <si>
+    <t>left</t>
+  </si>
+  <si>
+    <t>mid</t>
+  </si>
+  <si>
+    <t>right</t>
+  </si>
+  <si>
+    <t>trim</t>
+  </si>
+  <si>
+    <t>len</t>
+  </si>
+  <si>
+    <t>cont</t>
+  </si>
+  <si>
+    <t>find</t>
+  </si>
+  <si>
+    <t>sub</t>
+  </si>
+  <si>
     <t>E001</t>
   </si>
   <si>
@@ -319,6 +345,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>1.</t>
     </r>
     <r>
@@ -326,7 +360,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Convert all Employee Names into </t>
@@ -337,7 +371,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>UPPERCASE</t>
@@ -347,7 +381,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>.</t>
@@ -355,6 +389,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>2.</t>
     </r>
     <r>
@@ -362,7 +404,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Convert the Department names into </t>
@@ -373,7 +415,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>UPPERCASE</t>
@@ -383,7 +425,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>.</t>
@@ -394,6 +436,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>3.</t>
     </r>
     <r>
@@ -401,7 +451,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Convert all Employee Names into </t>
@@ -412,7 +462,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>lowercase</t>
@@ -422,7 +472,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>.</t>
@@ -430,6 +480,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>4.</t>
     </r>
     <r>
@@ -437,7 +495,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Convert all Email IDs into </t>
@@ -448,7 +506,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>lowercase</t>
@@ -458,7 +516,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>.</t>
@@ -469,6 +527,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>5.</t>
     </r>
     <r>
@@ -476,7 +542,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Convert the Employee Names into </t>
@@ -487,7 +553,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>Proper Case</t>
@@ -497,7 +563,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>.</t>
@@ -505,6 +571,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>6.</t>
     </r>
     <r>
@@ -512,7 +586,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Convert the Department names into </t>
@@ -523,7 +597,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>Proper Case</t>
@@ -533,7 +607,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>.</t>
@@ -544,6 +618,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>7.</t>
     </r>
     <r>
@@ -551,7 +633,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Extract the </t>
@@ -562,7 +644,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>first 3 characters</t>
@@ -572,7 +654,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> from each Employee Name.</t>
@@ -580,6 +662,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>8.</t>
     </r>
     <r>
@@ -587,7 +677,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Extract the </t>
@@ -598,7 +688,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>first 2 characters</t>
@@ -608,7 +698,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> from the Employee Code.</t>
@@ -616,6 +706,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>9.</t>
     </r>
     <r>
@@ -623,7 +721,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Extract the </t>
@@ -634,7 +732,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>first 2 characters</t>
@@ -644,7 +742,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> from each Email ID.</t>
@@ -655,6 +753,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>10.</t>
     </r>
     <r>
@@ -662,7 +768,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Extract the </t>
@@ -673,7 +779,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>employee number</t>
@@ -683,7 +789,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> from the Employee Code.</t>
@@ -694,6 +800,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
+      </rPr>
       <t>IT-2026-001</t>
     </r>
     <r>
@@ -701,7 +813,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> → </t>
@@ -711,12 +823,21 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
       </rPr>
       <t>2026</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>11.</t>
     </r>
     <r>
@@ -724,7 +845,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Extract the </t>
@@ -735,7 +856,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>year</t>
@@ -745,7 +866,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> from every Employee Code.</t>
@@ -753,6 +874,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>12.</t>
     </r>
     <r>
@@ -760,7 +889,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Extract the </t>
@@ -771,7 +900,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>department code</t>
@@ -781,7 +910,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> from the Employee Code.</t>
@@ -789,6 +918,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
+      </rPr>
       <t>HR-2026-003</t>
     </r>
     <r>
@@ -796,7 +931,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> → </t>
@@ -806,6 +941,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
       </rPr>
       <t>HR</t>
     </r>
@@ -815,6 +951,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>13.</t>
     </r>
     <r>
@@ -822,7 +966,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Extract the </t>
@@ -833,7 +977,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>last 3 characters</t>
@@ -843,7 +987,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> from the Employee Code.</t>
@@ -851,6 +995,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
+      </rPr>
       <t>IT-2026-001</t>
     </r>
     <r>
@@ -858,7 +1008,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> → </t>
@@ -868,12 +1018,21 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
       </rPr>
       <t>001</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>14.</t>
     </r>
     <r>
@@ -881,7 +1040,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Extract the </t>
@@ -892,7 +1051,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>last 4 digits</t>
@@ -902,7 +1061,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> from the Phone Number.</t>
@@ -910,6 +1069,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>15.</t>
     </r>
     <r>
@@ -917,7 +1084,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Extract the </t>
@@ -928,7 +1095,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>last 3 characters</t>
@@ -938,7 +1105,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> from each Employee Name.</t>
@@ -949,6 +1116,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>16.</t>
     </r>
     <r>
@@ -956,7 +1131,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Assume some employee names contain unnecessary spaces. Use </t>
@@ -966,6 +1141,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
       </rPr>
       <t>TRIM</t>
     </r>
@@ -974,7 +1150,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> to remove extra spaces.</t>
@@ -982,6 +1158,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
+      </rPr>
       <t>" anu kumari "</t>
     </r>
     <r>
@@ -989,7 +1171,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> → </t>
@@ -999,12 +1181,21 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
       </rPr>
       <t>"anu kumari"</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>17.</t>
     </r>
     <r>
@@ -1012,7 +1203,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Use </t>
@@ -1022,6 +1213,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
       </rPr>
       <t>TRIM</t>
     </r>
@@ -1030,7 +1222,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> to clean the Department names.</t>
@@ -1041,6 +1233,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>18.</t>
     </r>
     <r>
@@ -1048,7 +1248,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Find the </t>
@@ -1059,7 +1259,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>number of characters</t>
@@ -1069,7 +1269,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> in each Employee Name.</t>
@@ -1077,6 +1277,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>19.</t>
     </r>
     <r>
@@ -1084,7 +1292,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Find the </t>
@@ -1095,7 +1303,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>number of characters</t>
@@ -1105,7 +1313,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> in each Email ID.</t>
@@ -1113,6 +1321,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>20.</t>
     </r>
     <r>
@@ -1120,7 +1336,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Find the </t>
@@ -1131,7 +1347,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>number of characters</t>
@@ -1141,7 +1357,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> in each Employee Code.</t>
@@ -1152,6 +1368,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>21.</t>
     </r>
     <r>
@@ -1159,7 +1383,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Compare the Employee Name in row 2 with another cell containing </t>
@@ -1169,6 +1393,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
       </rPr>
       <t>anu kumari</t>
     </r>
@@ -1177,7 +1402,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">. Check whether they are </t>
@@ -1188,7 +1413,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>exactly the same</t>
@@ -1198,7 +1423,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>.</t>
@@ -1206,6 +1431,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>22.</t>
     </r>
     <r>
@@ -1213,7 +1446,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Compare two Employee Names and determine whether they are exactly identical, including </t>
@@ -1224,7 +1457,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>uppercase/lowercase differences</t>
@@ -1234,7 +1467,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>.</t>
@@ -1245,6 +1478,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>23.</t>
     </r>
     <r>
@@ -1252,7 +1493,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Combine </t>
@@ -1263,7 +1504,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>Employee ID + Employee Name</t>
@@ -1273,7 +1514,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>.</t>
@@ -1284,6 +1525,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>24.</t>
     </r>
     <r>
@@ -1291,7 +1540,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Combine </t>
@@ -1302,7 +1551,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>Employee Name + Department</t>
@@ -1312,7 +1561,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>.</t>
@@ -1323,6 +1572,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>25.</t>
     </r>
     <r>
@@ -1330,7 +1587,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Create a sentence using Employee Name and City.</t>
@@ -1344,6 +1601,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>26.</t>
     </r>
     <r>
@@ -1351,7 +1616,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Find the position of </t>
@@ -1361,6 +1626,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
       </rPr>
       <t>@</t>
     </r>
@@ -1369,7 +1635,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> in every Email ID.</t>
@@ -1377,6 +1643,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>27.</t>
     </r>
     <r>
@@ -1384,7 +1658,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Find the position of </t>
@@ -1394,6 +1668,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
       </rPr>
       <t>-</t>
     </r>
@@ -1402,7 +1677,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> in every Employee Code.</t>
@@ -1410,6 +1685,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>28.</t>
     </r>
     <r>
@@ -1417,7 +1700,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Find the position of the </t>
@@ -1428,7 +1711,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>first space</t>
@@ -1438,7 +1721,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> in each Employee Name.</t>
@@ -1449,6 +1732,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>29.</t>
     </r>
     <r>
@@ -1456,7 +1747,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Replace </t>
@@ -1466,6 +1757,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
       </rPr>
       <t>gmail.com</t>
     </r>
@@ -1474,7 +1766,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> with </t>
@@ -1484,6 +1776,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
       </rPr>
       <t>company.com</t>
     </r>
@@ -1492,7 +1785,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> in all Email IDs.</t>
@@ -1500,6 +1793,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
+      </rPr>
       <t>anu.kumari@gmail.com</t>
     </r>
     <r>
@@ -1507,7 +1806,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> → </t>
@@ -1517,12 +1816,21 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
       </rPr>
       <t>anu.kumari@company.com</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>30.</t>
     </r>
     <r>
@@ -1530,7 +1838,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Replace the hyphen </t>
@@ -1540,6 +1848,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
       </rPr>
       <t>-</t>
     </r>
@@ -1548,7 +1857,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> in Employee Codes with </t>
@@ -1558,6 +1867,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
       </rPr>
       <t>/</t>
     </r>
@@ -1566,7 +1876,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>.</t>
@@ -1574,6 +1884,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
+      </rPr>
       <t>IT-2026-001</t>
     </r>
     <r>
@@ -1581,7 +1897,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> → </t>
@@ -1591,6 +1907,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
+        <charset val="134"/>
       </rPr>
       <t>IT/2026/001</t>
     </r>
@@ -1599,13 +1916,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1613,7 +1936,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1621,7 +1944,7 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1629,24 +1952,354 @@
       <sz val="13.5"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1654,12 +2307,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1667,7 +2559,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1676,18 +2571,61 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1736,7 +2674,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1769,26 +2707,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1821,23 +2742,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1979,21 +2883,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CADDFFF-47E6-4B52-99D2-E93DCF362286}">
-  <dimension ref="A1:H157"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:T157"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="7" max="7" width="11.7777777777778"/>
+    <col min="9" max="9" width="14.5555555555556" customWidth="1"/>
+    <col min="17" max="17" width="16.7777777777778" customWidth="1"/>
+    <col min="19" max="19" width="27.1111111111111" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.8">
+    <row r="1" ht="28.8" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2018,715 +2923,1159 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="57.6">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" ht="57.6" spans="1:20">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="4">
+        <v>9876543210</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" t="str">
+        <f>UPPER(B2)</f>
+        <v>ANU KUMARI</v>
+      </c>
+      <c r="J2" t="str">
+        <f>LOWER(B2)</f>
+        <v>anu kumari</v>
+      </c>
+      <c r="K2" t="str">
+        <f>PROPER(B2)</f>
+        <v>Anu Kumari</v>
+      </c>
+      <c r="L2" t="str">
+        <f>LEFT(B2,3)</f>
+        <v>anu</v>
+      </c>
+      <c r="M2" t="str">
+        <f>MID(E2,9,3)</f>
+        <v>001</v>
+      </c>
+      <c r="N2" t="str">
+        <f>RIGHT(E2,3)</f>
+        <v>001</v>
+      </c>
+      <c r="O2" t="str">
+        <f>TRIM(B2)</f>
+        <v>anu kumari</v>
+      </c>
+      <c r="P2">
+        <f>LEN(B2)</f>
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="Q2" t="str">
+        <f>CONCATENATE(A2,B2)</f>
+        <v>E001anu kumari</v>
+      </c>
+      <c r="R2">
+        <f>FIND("@",F2)</f>
         <v>11</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="2">
-        <v>9876543210</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="43.2">
+      <c r="S2" t="str">
+        <f>SUBSTITUTE(F2,"gmail.com","company.com")</f>
+        <v>anu.kumari@company.com</v>
+      </c>
+      <c r="T2" t="b">
+        <f>EXACT(B2,"anu kumari")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="43.2" spans="1:20">
       <c r="A3" s="2" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G3" s="2">
         <v>9876543211</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="57.6">
+        <v>32</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" ref="I3:I13" si="0">UPPER(B3)</f>
+        <v>RAHUL MENON</v>
+      </c>
+      <c r="J3" t="str">
+        <f t="shared" ref="J3:J45" si="1">LOWER(B3)</f>
+        <v>rahul menon</v>
+      </c>
+      <c r="K3" t="str">
+        <f t="shared" ref="K3:K8" si="2">PROPER(B3)</f>
+        <v>Rahul Menon</v>
+      </c>
+      <c r="L3" t="str">
+        <f t="shared" ref="L3:L8" si="3">LEFT(B3,3)</f>
+        <v>RAH</v>
+      </c>
+      <c r="M3" t="str">
+        <f t="shared" ref="M3:M8" si="4">MID(E3,9,3)</f>
+        <v>002</v>
+      </c>
+      <c r="P3">
+        <f>LEN(B3)</f>
+        <v>11</v>
+      </c>
+      <c r="S3" t="str">
+        <f>SUBSTITUTE(F3,"gmail.com","company.com")</f>
+        <v>rahul.menon@company.com</v>
+      </c>
+    </row>
+    <row r="4" ht="43.2" spans="1:20">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="G4" s="2">
         <v>9876543212</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="57.6">
+        <v>39</v>
+      </c>
+      <c r="I4" t="str">
+        <f t="shared" si="0"/>
+        <v>MEERA NAIR</v>
+      </c>
+      <c r="J4" t="str">
+        <f t="shared" si="1"/>
+        <v>meera nair</v>
+      </c>
+      <c r="K4" t="str">
+        <f t="shared" si="2"/>
+        <v>Meera Nair</v>
+      </c>
+      <c r="L4" t="str">
+        <f t="shared" si="3"/>
+        <v>mee</v>
+      </c>
+      <c r="M4" t="str">
+        <f t="shared" si="4"/>
+        <v>003</v>
+      </c>
+      <c r="P4">
+        <f>LEN(B4)</f>
+        <v>10</v>
+      </c>
+      <c r="S4" t="str">
+        <f>SUBSTITUTE(F4,"gmail.com","company.com")</f>
+        <v>meera.nair@company.com</v>
+      </c>
+    </row>
+    <row r="5" ht="57.6" spans="1:20">
       <c r="A5" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="G5" s="2">
         <v>9876543213</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="43.2">
+        <v>45</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" si="0"/>
+        <v>ARUN KUMAR</v>
+      </c>
+      <c r="J5" t="str">
+        <f t="shared" si="1"/>
+        <v>arun kumar</v>
+      </c>
+      <c r="K5" t="str">
+        <f t="shared" si="2"/>
+        <v>Arun Kumar</v>
+      </c>
+      <c r="L5" t="str">
+        <f t="shared" si="3"/>
+        <v>Aru</v>
+      </c>
+      <c r="M5" t="str">
+        <f t="shared" si="4"/>
+        <v>004</v>
+      </c>
+      <c r="P5">
+        <f>LEN(B5)</f>
+        <v>10</v>
+      </c>
+      <c r="S5" t="str">
+        <f>SUBSTITUTE(F5,"gmail.com","company.com")</f>
+        <v>arun.kumar@company.com</v>
+      </c>
+    </row>
+    <row r="6" ht="43.2" spans="1:20">
       <c r="A6" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="G6" s="2">
         <v>9876543214</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="43.2">
+        <v>51</v>
+      </c>
+      <c r="I6" t="str">
+        <f t="shared" si="0"/>
+        <v>SNEHA JOSE</v>
+      </c>
+      <c r="J6" t="str">
+        <f t="shared" si="1"/>
+        <v>sneha jose</v>
+      </c>
+      <c r="K6" t="str">
+        <f t="shared" si="2"/>
+        <v>Sneha Jose</v>
+      </c>
+      <c r="L6" t="str">
+        <f t="shared" si="3"/>
+        <v>sne</v>
+      </c>
+      <c r="M6" t="str">
+        <f t="shared" si="4"/>
+        <v>005</v>
+      </c>
+      <c r="P6">
+        <f>LEN(B6)</f>
+        <v>10</v>
+      </c>
+      <c r="S6" t="str">
+        <f>SUBSTITUTE(F6,"gmail.com","company.com")</f>
+        <v>sneha.jose@company.com</v>
+      </c>
+    </row>
+    <row r="7" ht="43.2" spans="1:20">
       <c r="A7" s="2" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G7" s="2">
         <v>9876543215</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="57.6">
+        <v>58</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="0"/>
+        <v>VISHNU DAS</v>
+      </c>
+      <c r="J7" t="str">
+        <f t="shared" si="1"/>
+        <v>vishnu das</v>
+      </c>
+      <c r="K7" t="str">
+        <f t="shared" si="2"/>
+        <v>Vishnu Das</v>
+      </c>
+      <c r="L7" t="str">
+        <f t="shared" si="3"/>
+        <v>VIS</v>
+      </c>
+      <c r="M7" t="str">
+        <f t="shared" si="4"/>
+        <v>006</v>
+      </c>
+      <c r="P7">
+        <f>LEN(B7)</f>
+        <v>10</v>
+      </c>
+      <c r="S7" t="str">
+        <f>SUBSTITUTE(F7,"gmail.com","company.com")</f>
+        <v>vishnu.das@company.com</v>
+      </c>
+    </row>
+    <row r="8" ht="57.6" spans="1:20">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G8" s="2">
         <v>9876543216</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="43.2">
+        <v>32</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="0"/>
+        <v>DIYA ROY</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="1"/>
+        <v>diya roy</v>
+      </c>
+      <c r="K8" t="str">
+        <f t="shared" si="2"/>
+        <v>Diya Roy</v>
+      </c>
+      <c r="L8" t="str">
+        <f t="shared" si="3"/>
+        <v>diy</v>
+      </c>
+      <c r="M8" t="str">
+        <f t="shared" si="4"/>
+        <v>007</v>
+      </c>
+    </row>
+    <row r="9" ht="43.2" spans="1:20">
       <c r="A9" s="2" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G9" s="2">
         <v>9876543217</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="43.2">
+        <v>69</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="0"/>
+        <v>NIKHIL VARMA</v>
+      </c>
+      <c r="J9" t="str">
+        <f t="shared" si="1"/>
+        <v>nikhil varma</v>
+      </c>
+    </row>
+    <row r="10" ht="43.2" spans="1:20">
       <c r="A10" s="2" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="G10" s="2">
         <v>9876543218</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="43.2">
+        <v>25</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="0"/>
+        <v>FATHIMA ALI</v>
+      </c>
+      <c r="J10" t="str">
+        <f t="shared" si="1"/>
+        <v>fathima ali</v>
+      </c>
+    </row>
+    <row r="11" ht="43.2" spans="1:20">
       <c r="A11" s="2" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="G11" s="2">
         <v>9876543219</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="57.6">
+        <v>45</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="0"/>
+        <v>AKHIL RAJ</v>
+      </c>
+      <c r="J11" t="str">
+        <f t="shared" si="1"/>
+        <v>akhil raj</v>
+      </c>
+    </row>
+    <row r="12" ht="57.6" spans="1:20">
       <c r="A12" s="2" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="G12" s="2">
         <v>9876543220</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="43.2">
+        <v>39</v>
+      </c>
+      <c r="I12" t="str">
+        <f t="shared" si="0"/>
+        <v>LAKSHMI MENON</v>
+      </c>
+      <c r="J12" t="str">
+        <f t="shared" si="1"/>
+        <v>lakshmi menon</v>
+      </c>
+    </row>
+    <row r="13" ht="43.2" spans="1:20">
       <c r="A13" s="2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G13" s="2">
         <v>9876543221</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="43.2">
+        <v>32</v>
+      </c>
+      <c r="I13" t="str">
+        <f t="shared" si="0"/>
+        <v>SURESH BABU</v>
+      </c>
+      <c r="J13" t="str">
+        <f t="shared" si="1"/>
+        <v>suresh babu</v>
+      </c>
+    </row>
+    <row r="14" ht="43.2" spans="1:20">
       <c r="A14" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G14" s="2">
         <v>9876543222</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="43.2">
+        <v>69</v>
+      </c>
+      <c r="J14" t="str">
+        <f t="shared" si="1"/>
+        <v>neha krishnan</v>
+      </c>
+    </row>
+    <row r="15" ht="43.2" spans="1:20">
       <c r="A15" s="2" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="G15" s="2">
         <v>9876543223</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="57.6">
+        <v>51</v>
+      </c>
+      <c r="J15" t="str">
+        <f t="shared" si="1"/>
+        <v>manu mohan</v>
+      </c>
+    </row>
+    <row r="16" ht="57.6" spans="1:20">
       <c r="A16" s="2" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="G16" s="2">
         <v>9876543224</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="18">
-      <c r="A17" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" ht="18">
-      <c r="A25" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" ht="18">
-      <c r="A33" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" ht="18">
-      <c r="A41" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J16" t="str">
+        <f t="shared" si="1"/>
+        <v>riya paul</v>
+      </c>
+    </row>
+    <row r="17" ht="18" spans="1:10">
+      <c r="A17" s="5" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="5" t="s">
+      <c r="J17" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="J18" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="6" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" ht="18">
-      <c r="A51" s="4" t="s">
+      <c r="J19" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="J20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="6" t="s">
         <v>106</v>
       </c>
+      <c r="J21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="J22" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="J23" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="J24" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="18" spans="1:10">
+      <c r="A25" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="J25" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="J26" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="J27" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="J28" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="J29" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="J30" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="J31" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="J32" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="18" spans="1:10">
+      <c r="A33" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J33" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="J34" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="J35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="J36" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="J37" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="J38" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="J39" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="J40" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="18" spans="1:10">
+      <c r="A41" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="J41" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="J42" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="J43" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="J44" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="J45" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="51" ht="18" spans="1:1">
+      <c r="A51" s="5" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="5" t="s">
-        <v>107</v>
+      <c r="A53" s="6" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="6" t="s">
-        <v>109</v>
+      <c r="A57" s="7" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="5" t="s">
-        <v>110</v>
+      <c r="A59" s="6" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="5" t="s">
-        <v>111</v>
+      <c r="A61" s="6" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" ht="18">
-      <c r="A69" s="4" t="s">
-        <v>113</v>
+      <c r="A65" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="69" ht="18" spans="1:1">
+      <c r="A69" s="5" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="5" t="s">
-        <v>114</v>
+      <c r="A71" s="6" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" s="6" t="s">
-        <v>115</v>
+      <c r="A75" s="7" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" s="5" t="s">
-        <v>116</v>
+      <c r="A77" s="6" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="5" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" ht="18">
-      <c r="A83" s="4" t="s">
-        <v>118</v>
+      <c r="A79" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="83" ht="18" spans="1:1">
+      <c r="A83" s="5" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="85" spans="1:1">
-      <c r="A85" s="5" t="s">
-        <v>119</v>
+      <c r="A85" s="6" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="89" spans="1:1">
-      <c r="A89" s="6" t="s">
-        <v>120</v>
+      <c r="A89" s="7" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="91" spans="1:1">
-      <c r="A91" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" ht="18">
-      <c r="A95" s="4" t="s">
-        <v>122</v>
+      <c r="A91" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="95" ht="18" spans="1:1">
+      <c r="A95" s="5" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" s="5" t="s">
-        <v>123</v>
+      <c r="A97" s="6" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" s="5" t="s">
-        <v>124</v>
+      <c r="A99" s="6" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" ht="18">
-      <c r="A105" s="4" t="s">
-        <v>126</v>
+      <c r="A101" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="105" ht="18" spans="1:1">
+      <c r="A105" s="5" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="107" spans="1:1">
-      <c r="A107" s="5" t="s">
-        <v>127</v>
+      <c r="A107" s="6" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="109" spans="1:1">
-      <c r="A109" s="5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" ht="18">
-      <c r="A113" s="4" t="s">
-        <v>129</v>
+      <c r="A109" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="113" ht="18" spans="1:1">
+      <c r="A113" s="5" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="115" spans="1:1">
-      <c r="A115" s="5" t="s">
-        <v>130</v>
+      <c r="A115" s="6" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="119" spans="1:1">
-      <c r="A119" s="6" t="s">
-        <v>131</v>
+      <c r="A119" s="7" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="121" spans="1:1">
-      <c r="A121" s="5" t="s">
-        <v>132</v>
+      <c r="A121" s="6" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="125" spans="1:1">
-      <c r="A125" s="6" t="s">
-        <v>133</v>
+      <c r="A125" s="7" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="127" spans="1:1">
-      <c r="A127" s="5" t="s">
-        <v>134</v>
+      <c r="A127" s="6" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="131" spans="1:1">
-      <c r="A131" s="6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1" ht="18">
-      <c r="A135" s="4" t="s">
-        <v>136</v>
+      <c r="A131" s="7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="135" ht="18" spans="1:1">
+      <c r="A135" s="5" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="137" spans="1:1">
-      <c r="A137" s="5" t="s">
-        <v>137</v>
+      <c r="A137" s="6" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="139" spans="1:1">
-      <c r="A139" s="5" t="s">
-        <v>138</v>
+      <c r="A139" s="6" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="141" spans="1:1">
-      <c r="A141" s="5" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1" ht="18">
-      <c r="A145" s="4" t="s">
-        <v>140</v>
+      <c r="A141" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="145" ht="18" spans="1:1">
+      <c r="A145" s="5" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="147" spans="1:1">
-      <c r="A147" s="5" t="s">
-        <v>141</v>
+      <c r="A147" s="6" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="151" spans="1:1">
-      <c r="A151" s="6" t="s">
-        <v>142</v>
+      <c r="A151" s="7" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="153" spans="1:1">
-      <c r="A153" s="5" t="s">
-        <v>143</v>
+      <c r="A153" s="6" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="157" spans="1:1">
-      <c r="A157" s="6" t="s">
-        <v>144</v>
+      <c r="A157" s="7" t="s">
+        <v>155</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="mailto:anu.kumari@gmail.com" xr:uid="{17772736-4FBE-4042-8625-C41743053DF2}"/>
-    <hyperlink ref="F3" r:id="rId2" display="mailto:rahul.menon@gmail.com" xr:uid="{72A3BFA6-E420-40FD-8896-E29FBCD063F8}"/>
-    <hyperlink ref="F4" r:id="rId3" display="mailto:meera.nair@gmail.com" xr:uid="{FB125A9B-4B61-41EF-A1C4-9F27B101ADA3}"/>
-    <hyperlink ref="F5" r:id="rId4" display="mailto:arun.kumar@gmail.com" xr:uid="{DD852542-08FD-4D81-B82A-CF1672696B3A}"/>
-    <hyperlink ref="F6" r:id="rId5" display="mailto:sneha.jose@gmail.com" xr:uid="{E8B9EA4E-2AEB-4A44-B6D5-3F3391F3B671}"/>
-    <hyperlink ref="F7" r:id="rId6" display="mailto:vishnu.das@gmail.com" xr:uid="{03190A32-092A-419D-AA8F-B337BF19FE1F}"/>
-    <hyperlink ref="F8" r:id="rId7" display="mailto:diya.roy@gmail.com" xr:uid="{2E47AEB9-7091-41A6-B208-3097785601EC}"/>
-    <hyperlink ref="F9" r:id="rId8" display="mailto:nikhil.varma@gmail.com" xr:uid="{6A449B8F-68D1-4B95-BA78-E3F9D0BD8A31}"/>
-    <hyperlink ref="F10" r:id="rId9" display="mailto:fathima.ali@gmail.com" xr:uid="{32162B2E-1BD4-4A15-9471-19D7E9A6AC36}"/>
-    <hyperlink ref="F11" r:id="rId10" display="mailto:akhil.raj@gmail.com" xr:uid="{90A9D697-CB82-4EDB-91AC-2E70722F89B6}"/>
-    <hyperlink ref="F12" r:id="rId11" display="mailto:lakshmi.menon@gmail.com" xr:uid="{9C3D0A3F-7AF8-415B-A1CC-7D6F55614E3C}"/>
-    <hyperlink ref="F13" r:id="rId12" display="mailto:suresh.babu@gmail.com" xr:uid="{534A8912-052B-4166-A3F5-57B97EC88604}"/>
-    <hyperlink ref="F14" r:id="rId13" display="mailto:neha.krishnan@gmail.com" xr:uid="{586630C8-37A4-4D03-BD50-2A0031B8B9F2}"/>
-    <hyperlink ref="F15" r:id="rId14" display="mailto:manu.mohan@gmail.com" xr:uid="{5E1509AD-2F7F-4BC1-99BB-65BFA8B4465E}"/>
-    <hyperlink ref="F16" r:id="rId15" display="mailto:riya.paul@gmail.com" xr:uid="{A26B7233-B426-40E3-ADAE-4BF64ADBF686}"/>
+    <hyperlink ref="F2" r:id="rId1" display="anu.kumari@gmail.com"/>
+    <hyperlink ref="F3" r:id="rId2" display="rahul.menon@gmail.com"/>
+    <hyperlink ref="F4" r:id="rId3" display="meera.nair@gmail.com"/>
+    <hyperlink ref="F5" r:id="rId4" display="arun.kumar@gmail.com"/>
+    <hyperlink ref="F6" r:id="rId5" display="sneha.jose@gmail.com"/>
+    <hyperlink ref="F7" r:id="rId6" display="vishnu.das@gmail.com"/>
+    <hyperlink ref="F8" r:id="rId7" display="diya.roy@gmail.com"/>
+    <hyperlink ref="F9" r:id="rId8" display="nikhil.varma@gmail.com"/>
+    <hyperlink ref="F10" r:id="rId9" display="fathima.ali@gmail.com"/>
+    <hyperlink ref="F11" r:id="rId10" display="akhil.raj@gmail.com"/>
+    <hyperlink ref="F12" r:id="rId11" display="lakshmi.menon@gmail.com"/>
+    <hyperlink ref="F13" r:id="rId12" display="suresh.babu@gmail.com"/>
+    <hyperlink ref="F14" r:id="rId13" display="neha.krishnan@gmail.com"/>
+    <hyperlink ref="F15" r:id="rId14" display="manu.mohan@gmail.com"/>
+    <hyperlink ref="F16" r:id="rId15" display="riya.paul@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>